--- a/backend/backups/category13_professional_business_services_FINAL.xlsx
+++ b/backend/backups/category13_professional_business_services_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,165 +425,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2cd29d58-974c-5481-bb7a-20c2fd20c3ad</t>
+          <t>ad4f532c-aea7-5ce6-bddd-dd125105681c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Accounting &amp; Tax Filing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Accounting &amp; Tax Filing Premium Care Option 14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1300</v>
+        <v>3399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.967987+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.967987+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2b7f005f-3cf0-5b92-be1f-91e92107b03b</t>
+          <t>d3f326d6-8dc2-577e-bdef-e60143df9966</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Accounting &amp; Tax Filing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Accounting &amp; Tax Filing Premium Care Option 18</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1600</v>
+        <v>3799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.971446+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.971446+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -612,195 +603,215 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Accounting &amp; Tax Filing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Accounting &amp; Tax Filing Premium Care Option 8</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1900</v>
+        <v>2799</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.973874+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.973874+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ad4f532c-aea7-5ce6-bddd-dd125105681c</t>
+          <t>23128b73-d2c7-5b86-b93e-348146159bf3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 4</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Rental Agreement &amp; Property E-Stamping</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2200</v>
+        <v>599</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Legal draft creation, e-stamp paper purchase, and doorstep delivery of rental contract.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Rental Agreement &amp; Property E-Stamping procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Rental Agreement &amp; Property E-Stamping procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.976845+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.976845+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Rental Agreement &amp; Property E-Stamping take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1c8638eb-082d-5308-9752-656c4a57feb2</t>
+          <t>d127f9d4-f583-5a22-a8a4-8e1760ff3989</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 5</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Business Consulting</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Business Consulting Premium Care Option 17</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2500</v>
+        <v>3699</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Business Consulting Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Business Consulting Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.979393+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.979393+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d3f326d6-8dc2-577e-bdef-e60143df9966</t>
+          <t>6f614ed0-0baa-546b-9043-4232647dedd3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Service Variation 6</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Business Consulting</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing</t>
+          <t>Business Consulting Premium Care Option 5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2800</v>
+        <v>2499</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Business Consulting Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional accounting &amp; tax filing service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Accounting &amp; Tax Filing professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Business Consulting Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.982178+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.982178+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -812,1145 +823,1260 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Business Consulting Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Business Consulting</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Business Consulting</t>
+          <t>Business Consulting Premium Care Option 7</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1300</v>
+        <v>2699</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Business Consulting Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional business consulting service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Business Consulting professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Business Consulting Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.984181+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.984181+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0cfc0d33-6962-5101-897a-b6e467f1a839</t>
+          <t>23cc4d79-35aa-5559-b8f2-5fa3c1e267f3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Business Consulting Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Career Services</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Business Consulting</t>
+          <t>Executive Resume &amp; LinkedIn Profile Rewrite</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1600</v>
+        <v>1299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>ATS-friendly modern resume design highlighting key achievements and keywords for job seekers.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Executive Resume &amp; LinkedIn Profile Rewrite procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional business consulting service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Business Consulting professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Executive Resume &amp; LinkedIn Profile Rewrite procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.986215+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.986215+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Executive Resume &amp; LinkedIn Profile Rewrite take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23128b73-d2c7-5b86-b93e-348146159bf3</t>
+          <t>2cd29d58-974c-5481-bb7a-20c2fd20c3ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Business Consulting Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Business Consulting</t>
+          <t>Bookkeeping &amp; Tally Accounting Support</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1900</v>
+        <v>2999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Monthly sales ledger entry, bank reconciliation, and profit/loss statement generation.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Bookkeeping &amp; Tally Accounting Support procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional business consulting service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Business Consulting professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Bookkeeping &amp; Tally Accounting Support procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.988665+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.988665+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Bookkeeping &amp; Tally Accounting Support take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6f614ed0-0baa-546b-9043-4232647dedd3</t>
+          <t>10cfb48f-7861-5bd8-b9e2-af03fc2233da</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Business Consulting Service Variation 4</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Business Consulting</t>
+          <t>GST Registration &amp; Monthly Compliance Filing</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2200</v>
+        <v>1499</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>New GSTIN application, document verification, and filing GSTR-1 / GSTR-3B returns.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional GST Registration &amp; Monthly Compliance Filing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional business consulting service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Business Consulting professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete GST Registration &amp; Monthly Compliance Filing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.990910+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.990910+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does GST Registration &amp; Monthly Compliance Filing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>d127f9d4-f583-5a22-a8a4-8e1760ff3989</t>
+          <t>0cfc0d33-6962-5101-897a-b6e467f1a839</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Business Consulting Service Variation 5</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Business Consulting</t>
+          <t>Income Tax Return (ITR) Filing for Salaried</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2500</v>
+        <v>799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>CA-verified Form-16 computation, tax-saving deduction claims under 80C/80D, and e-filing.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Income Tax Return (ITR) Filing for Salaried procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional business consulting service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Business Consulting professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Income Tax Return (ITR) Filing for Salaried procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.993905+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.993905+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Income Tax Return (ITR) Filing for Salaried take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12e4d8b4-323b-5f07-894b-bcd929375dac</t>
+          <t>2b7f005f-3cf0-5b92-be1f-91e92107b03b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Legal Documentation Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Legal Documentation</t>
+          <t>FSSAI Food License Registration for Cloud Kitchens</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>1199</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Basic or State FSSAI license documentation and online submission for restaurants &amp; home bakers.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional FSSAI Food License Registration for Cloud Kitchens procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional legal documentation service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Legal Documentation professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete FSSAI Food License Registration for Cloud Kitchens procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.996268+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.996268+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does FSSAI Food License Registration for Cloud Kitchens take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9a1c47e9-1b86-587c-8ffc-0f5b6d2f0b2f</t>
+          <t>12e4d8b4-323b-5f07-894b-bcd929375dac</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Legal Documentation Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Legal Documentation</t>
+          <t>Private Limited Company Registration Package</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1600</v>
+        <v>4999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>DSC, DIN, Name approval, MOA/AOA drafting, and MCA incorporation certificate setup.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Private Limited Company Registration Package procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional legal documentation service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Legal Documentation professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Private Limited Company Registration Package procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.998577+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.998577+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Private Limited Company Registration Package take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23cc4d79-35aa-5559-b8f2-5fa3c1e267f3</t>
+          <t>1c8638eb-082d-5308-9752-656c4a57feb2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Legal Documentation Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Legal Documentation</t>
+          <t>Trademark Brand Name &amp; Logo Filing</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1900</v>
+        <v>2499</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Comprehensive trademark availability search and online government TM application submission.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Trademark Brand Name &amp; Logo Filing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional legal documentation service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Legal Documentation professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Trademark Brand Name &amp; Logo Filing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.001299+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.001299+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Trademark Brand Name &amp; Logo Filing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>df9cfe85-1d0a-5f3e-a166-ee049aae2d6f</t>
+          <t>9a1c47e9-1b86-587c-8ffc-0f5b6d2f0b2f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Legal Documentation Service Variation 4</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal Documentation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Legal Documentation</t>
+          <t>Legal Documentation Premium Care Option 11</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2200</v>
+        <v>3099</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Legal Documentation Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional legal documentation service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Legal Documentation professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Legal Documentation Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.003406+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.003406+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>54da5a3b-5e07-578c-93eb-f101c7e6f75a</t>
+          <t>df9cfe85-1d0a-5f3e-a166-ee049aae2d6f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Legal Documentation Service Variation 5</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal Documentation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Legal Documentation</t>
+          <t>Legal Documentation Premium Care Option 19</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2500</v>
+        <v>3899</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Legal Documentation Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional legal documentation service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Legal Documentation professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Legal Documentation Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.005522+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.005522+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6fc3fc66-517c-5e02-bfe4-bc46992ce52f</t>
+          <t>54da5a3b-5e07-578c-93eb-f101c7e6f75a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Legal Documentation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Legal Documentation Premium Care Option 3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1300</v>
+        <v>2299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Legal Documentation Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Legal Documentation Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.008120+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.008120+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4b02dc00-0e2a-5cac-9625-dd74a89b9f92</t>
+          <t>2f1f5635-323c-5512-bdc9-6f910785f38d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Marketing &amp; Branding</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Marketing &amp; Branding Premium Care Option 1</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1600</v>
+        <v>2099</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Marketing &amp; Branding Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Marketing &amp; Branding Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.010360+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.010360+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2f1f5635-323c-5512-bdc9-6f910785f38d</t>
+          <t>87d437f2-8c00-5a42-baae-ab2bc2de39c2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Marketing &amp; Branding</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Marketing &amp; Branding Premium Care Option 10</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1900</v>
+        <v>2999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Marketing &amp; Branding Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Marketing &amp; Branding Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.013500+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.013500+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>87d437f2-8c00-5a42-baae-ab2bc2de39c2</t>
+          <t>b5926d2c-89c0-5b8f-802c-6e6c6a6408f5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 4</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Marketing &amp; Branding</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Marketing &amp; Branding Premium Care Option 15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2200</v>
+        <v>3499</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Marketing &amp; Branding Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Marketing &amp; Branding Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.015700+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.015700+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b5926d2c-89c0-5b8f-802c-6e6c6a6408f5</t>
+          <t>4b02dc00-0e2a-5cac-9625-dd74a89b9f92</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 5</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Marketing &amp; Branding</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Marketing &amp; Branding Premium Care Option 2</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2500</v>
+        <v>2199</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Marketing &amp; Branding Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Marketing &amp; Branding Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.018003+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.018003+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10cfb48f-7861-5bd8-b9e2-af03fc2233da</t>
+          <t>6fc3fc66-517c-5e02-bfe4-bc46992ce52f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Service Variation 6</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Marketing &amp; Branding</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding</t>
+          <t>Marketing &amp; Branding Premium Care Option 6</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2800</v>
+        <v>2599</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Marketing &amp; Branding Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional marketing &amp; branding service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Marketing &amp; Branding professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Marketing &amp; Branding Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.020635+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.020635+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f2de5783-e16d-5c82-8474-430e0e7015cc</t>
+          <t>ab3bf40b-aff5-52aa-9831-424bf0c61fbf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Staffing &amp; HR Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services</t>
+          <t>Staffing &amp; HR Services Premium Care Option 13</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1300</v>
+        <v>3299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Staffing &amp; HR Services Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional staffing &amp; hr services service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Staffing &amp; HR Services professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Staffing &amp; HR Services Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.022693+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.022693+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7eb034ef-66d5-5be7-9fb2-4cabe9ff84fe</t>
+          <t>b61d0d45-f019-5134-9763-b69b75b59bd6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Staffing &amp; HR Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services</t>
+          <t>Staffing &amp; HR Services Premium Care Option 16</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1600</v>
+        <v>3599</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Staffing &amp; HR Services Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional staffing &amp; hr services service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Staffing &amp; HR Services professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Staffing &amp; HR Services Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.024996+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.024996+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>b61d0d45-f019-5134-9763-b69b75b59bd6</t>
+          <t>ef6118e1-648b-5c1a-babf-6f4a12842388</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Staffing &amp; HR Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services</t>
+          <t>Staffing &amp; HR Services Premium Care Option 20</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1900</v>
+        <v>3999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Staffing &amp; HR Services Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional staffing &amp; hr services service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Staffing &amp; HR Services professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Staffing &amp; HR Services Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.027640+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.027640+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ef6118e1-648b-5c1a-babf-6f4a12842388</t>
+          <t>f2de5783-e16d-5c82-8474-430e0e7015cc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Service Variation 4</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Staffing &amp; HR Services</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services</t>
+          <t>Staffing &amp; HR Services Premium Care Option 21</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2200</v>
+        <v>4099</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Staffing &amp; HR Services Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional staffing &amp; hr services service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Staffing &amp; HR Services professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Staffing &amp; HR Services Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.029750+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.029750+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ab3bf40b-aff5-52aa-9831-424bf0c61fbf</t>
+          <t>7eb034ef-66d5-5be7-9fb2-4cabe9ff84fe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Service Variation 5</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Staffing &amp; HR Services</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services</t>
+          <t>Staffing &amp; HR Services Premium Care Option 9</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2500</v>
+        <v>2899</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Staffing &amp; HR Services Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional staffing &amp; hr services service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Staffing &amp; HR Services professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Staffing &amp; HR Services Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.032144+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.032144+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fc349e90-de34-59fc-a437-c73f56d5008e</t>
+          <t>a769d4ee-7b87-569a-9bf1-27212e4a71d9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Virtual Assistant Service Variation 1</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Virtual Assistant</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Virtual Assistant</t>
+          <t>Virtual Assistant Premium Care Option 12</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1300</v>
+        <v>3199</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Virtual Assistant Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional virtual assistant service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Virtual Assistant professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Virtual Assistant Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.034320+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.034320+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a769d4ee-7b87-569a-9bf1-27212e4a71d9</t>
+          <t>fc349e90-de34-59fc-a437-c73f56d5008e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Virtual Assistant Service Variation 2</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Virtual Assistant</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Virtual Assistant</t>
+          <t>Virtual Assistant Premium Care Option 22</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1600</v>
+        <v>4199</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Virtual Assistant Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional virtual assistant service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Virtual Assistant professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Virtual Assistant Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.036479+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.036479+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1962,45 +2088,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Virtual Assistant Service Variation 3</t>
+          <t>13. Professional &amp; Business Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13. Professional &amp; Business Services</t>
+          <t>Virtual Assistant</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Virtual Assistant</t>
+          <t>Virtual Assistant Premium Care Option 4</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1900</v>
+        <v>2399</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Initial consultation and needs assessment", "Service delivery within agreed timeline", "One round of revisions", "Final documentation and handover"]</t>
+          <t>['Professional Virtual Assistant Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional virtual assistant service to help your business grow and stay compliant.", "type": "description"}, {"type": "highlights", "items": ["Experienced Virtual Assistant professionals", "Government-compliant processes", "Confidential and secure handling", "Dedicated account manager"]}, {"type": "excluded_scope", "items": ["Government filing fees or registration charges", "Third-party software subscriptions"]}, {"type": "process_steps", "steps": [{"title": "Requirement Analysis", "description": "Understanding the business challenge or compliance requirement", "step_number": 1}, {"title": "Scope Definition", "description": "Defining deliverables, timelines, and pricing", "step_number": 2}, {"title": "Service Delivery", "description": "Executing the agreed professional service", "step_number": 3}, {"title": "Review &amp; Revision", "description": "Incorporating client feedback and finalising output", "step_number": 4}, {"title": "Handover &amp; Documentation", "description": "Delivering all outputs and supporting documentation", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["File all received documents securely", "Schedule follow-up compliance reviews annually"]}, {"type": "tools_materials", "tools": ["Professional software (Tally, MS Office, etc.)", "Legal databases", "Secure document portal", "CRM tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide all relevant business documents upfront", "Assign a point of contact for queries", "Ensure digital access for required portals"]}, {"type": "expected_results", "items": "Compliant, efficient, and growth-ready business operations."}, {"type": "important_notes", "items": "All services are subject to applicable government regulations and timelines."}, {"type": "warranty", "details": "Free revision within 7 days if deliverables do not meet agreed specifications.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, we follow strict NDAs and data privacy protocols for all client engagements.", "question": "Is my business data kept confidential?"}, {"answer": "Yes, we offer affordable packages specifically designed for startups and SMEs.", "question": "Do you work with startups?"}, {"answer": "Standard services take 3-7 business days; complex engagements may take longer.", "question": "How long does service delivery take?"}, {"answer": "Absolutely — contact us to build a custom bundle tailored to your business needs.", "question": "Can I get a custom package?"}]}, {"type": "tips", "items": ["Keep your tax filings up to date to avoid penalties."]}, {"dos": ["Share complete and accurate information for faster processing."], "type": "dos_donts", "donts": ["Do not delay statutory filings — late fees can be substantial."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Virtual Assistant Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.039133+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.039133+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category13_professional_business_services_FINAL.xlsx
+++ b/backend/backups/category13_professional_business_services_FINAL.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ad4f532c-aea7-5ce6-bddd-dd125105681c</t>
+          <t>787578c0-5d5a-5d2d-b2da-6642691a6ac6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,40 +503,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Premium Care Option 14</t>
+          <t>Annual Corporate Balance Sheet Audit Filing</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3399</v>
+        <v>4999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
+          <t>Statutory balance sheet compilation, P&amp;L audit report, and ROC compliance filing.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Annual Corporate Balance Sheet Audit Filing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Annual Corporate Balance Sheet Audit Filing procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 180 minutes.', 'question': 'How long does Annual Corporate Balance Sheet Audit Filing take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -558,47 +558,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Premium Care Option 18</t>
+          <t>Personal Capital Gains Tax Computation (Shares/Property)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3799</v>
+        <v>1799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
+          <t>Long-term and short-term capital gain calculations, indexation benefit, and tax exemptions.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Personal Capital Gains Tax Computation (Shares/Property) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Personal Capital Gains Tax Computation (Shares/Property) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Personal Capital Gains Tax Computation (Shares/Property) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>787578c0-5d5a-5d2d-b2da-6642691a6ac6</t>
+          <t>ad4f532c-aea7-5ce6-bddd-dd125105681c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -613,40 +613,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Accounting &amp; Tax Filing Premium Care Option 8</t>
+          <t>TDS Quarterly Return Filing (Form 24Q / 26Q)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2799</v>
+        <v>1499</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Specialized high-end Accounting &amp; Tax Filing service tailored to specific client needs with extended guarantee.</t>
+          <t>Computing vendor and employee TDS deductions, generating challans, and filing NSDL returns.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['Professional Accounting &amp; Tax Filing Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional TDS Quarterly Return Filing (Form 24Q / 26Q) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['Complete Accounting &amp; Tax Filing Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete TDS Quarterly Return Filing (Form 24Q / 26Q) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Accounting &amp; Tax Filing Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does TDS Quarterly Return Filing (Form 24Q / 26Q) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -723,47 +723,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Business Consulting Premium Care Option 17</t>
+          <t>Franchise Business Model &amp; Standard Operating Procedures</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3699</v>
+        <v>6999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
+          <t>Drafting operational manuals, franchise royalty agreements, and quality control checklists.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>['Professional Business Consulting Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Franchise Business Model &amp; Standard Operating Procedures procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['Complete Business Consulting Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Franchise Business Model &amp; Standard Operating Procedures procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 240 minutes.', 'question': 'How long does Franchise Business Model &amp; Standard Operating Procedures take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6f614ed0-0baa-546b-9043-4232647dedd3</t>
+          <t>76ca2a3d-a2c3-58bc-8e15-647ecbc18831</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -778,47 +778,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Business Consulting Premium Care Option 5</t>
+          <t>Market Entry &amp; Competitor Benchmarking Strategy</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2499</v>
+        <v>4499</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
+          <t>Detailed industry landscape report highlighting pricing models, customer pain points, and gaps.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>['Professional Business Consulting Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Market Entry &amp; Competitor Benchmarking Strategy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['Complete Business Consulting Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Market Entry &amp; Competitor Benchmarking Strategy procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 150 minutes.', 'question': 'How long does Market Entry &amp; Competitor Benchmarking Strategy take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>76ca2a3d-a2c3-58bc-8e15-647ecbc18831</t>
+          <t>6f614ed0-0baa-546b-9043-4232647dedd3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,40 +833,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Business Consulting Premium Care Option 7</t>
+          <t>Startup Pitch Deck &amp; Financial Modeling Review</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2699</v>
+        <v>3999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Specialized high-end Business Consulting service tailored to specific client needs with extended guarantee.</t>
+          <t>Reviewing 10-slide investor deck, 3-year revenue projections, and unit economics metrics.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Professional Business Consulting Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Startup Pitch Deck &amp; Financial Modeling Review procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>['Complete Business Consulting Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Startup Pitch Deck &amp; Financial Modeling Review procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Business Consulting Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Startup Pitch Deck &amp; Financial Modeling Review take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1273,47 +1273,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Legal Documentation Premium Care Option 11</t>
+          <t>Employment Offer Letter &amp; HR Policy Handbook Drafting</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3099</v>
+        <v>2499</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
+          <t>Drafting offer contracts, non-compete clauses, leave policies, and code of conduct.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['Professional Legal Documentation Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Employment Offer Letter &amp; HR Policy Handbook Drafting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['Complete Legal Documentation Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Employment Offer Letter &amp; HR Policy Handbook Drafting procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Employment Offer Letter &amp; HR Policy Handbook Drafting take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>df9cfe85-1d0a-5f3e-a166-ee049aae2d6f</t>
+          <t>54da5a3b-5e07-578c-93eb-f101c7e6f75a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,47 +1328,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Legal Documentation Premium Care Option 19</t>
+          <t>Non-Disclosure Agreement (NDA) &amp; Vendor Contract Drafting</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3899</v>
+        <v>1499</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
+          <t>Customized legally binding confidentiality and vendor service-level agreements.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['Professional Legal Documentation Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Non-Disclosure Agreement (NDA) &amp; Vendor Contract Drafting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Complete Legal Documentation Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Non-Disclosure Agreement (NDA) &amp; Vendor Contract Drafting procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Non-Disclosure Agreement (NDA) &amp; Vendor Contract Drafting take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>54da5a3b-5e07-578c-93eb-f101c7e6f75a</t>
+          <t>df9cfe85-1d0a-5f3e-a166-ee049aae2d6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1383,47 +1383,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Legal Documentation Premium Care Option 3</t>
+          <t>Power of Attorney (POA) &amp; Affidavit Legal Preparation</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2299</v>
+        <v>999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Specialized high-end Legal Documentation service tailored to specific client needs with extended guarantee.</t>
+          <t>General or special power of attorney drafting with notary stamp coordination.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['Professional Legal Documentation Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Power of Attorney (POA) &amp; Affidavit Legal Preparation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Complete Legal Documentation Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Power of Attorney (POA) &amp; Affidavit Legal Preparation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Legal Documentation Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Power of Attorney (POA) &amp; Affidavit Legal Preparation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2f1f5635-323c-5512-bdc9-6f910785f38d</t>
+          <t>6fc3fc66-517c-5e02-bfe4-bc46992ce52f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1438,47 +1438,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Premium Care Option 1</t>
+          <t>Complete Brand Identity Design (Logo, Palette, Fonts)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2099</v>
+        <v>3999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
+          <t>3 unique vector logo concepts, color guideline document, and business card layout.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['Professional Marketing &amp; Branding Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Complete Brand Identity Design (Logo, Palette, Fonts) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['Complete Marketing &amp; Branding Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Complete Brand Identity Design (Logo, Palette, Fonts) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 150 minutes.', 'question': 'How long does Complete Brand Identity Design (Logo, Palette, Fonts) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>87d437f2-8c00-5a42-baae-ab2bc2de39c2</t>
+          <t>2f1f5635-323c-5512-bdc9-6f910785f38d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Premium Care Option 10</t>
+          <t>Google Ads (PPC) Campaign Setup &amp; Keyword Audit</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1501,32 +1501,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
+          <t>Negative keyword filtering, search ad copy creation, and conversion tracking tag setup.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>['Professional Marketing &amp; Branding Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Google Ads (PPC) Campaign Setup &amp; Keyword Audit procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['Complete Marketing &amp; Branding Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Google Ads (PPC) Campaign Setup &amp; Keyword Audit procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Google Ads (PPC) Campaign Setup &amp; Keyword Audit take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Premium Care Option 15</t>
+          <t>Influencer Marketing Outreach &amp; Campaign Management</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
+          <t>Shortlisting niche micro-influencers, negotiating barter/paid rates, and campaign tracking.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>['Professional Marketing &amp; Branding Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Influencer Marketing Outreach &amp; Campaign Management procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>['Complete Marketing &amp; Branding Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Influencer Marketing Outreach &amp; Campaign Management procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Influencer Marketing Outreach &amp; Campaign Management take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1603,47 +1603,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Premium Care Option 2</t>
+          <t>Instagram &amp; Facebook Meta Ads Lead Generation Setup</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2199</v>
+        <v>2499</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
+          <t>Targeting high-intent demographics, lookalike audiences, and creative carousel ads.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>['Professional Marketing &amp; Branding Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Instagram &amp; Facebook Meta Ads Lead Generation Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['Complete Marketing &amp; Branding Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Instagram &amp; Facebook Meta Ads Lead Generation Setup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Instagram &amp; Facebook Meta Ads Lead Generation Setup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6fc3fc66-517c-5e02-bfe4-bc46992ce52f</t>
+          <t>87d437f2-8c00-5a42-baae-ab2bc2de39c2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1658,47 +1658,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Marketing &amp; Branding Premium Care Option 6</t>
+          <t>SEO On-Page Optimization &amp; Schema Markup</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2599</v>
+        <v>2499</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Specialized high-end Marketing &amp; Branding service tailored to specific client needs with extended guarantee.</t>
+          <t>Meta titles, H1 tags, alt tags, and JSON-LD local business schema deployment.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>['Professional Marketing &amp; Branding Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional SEO On-Page Optimization &amp; Schema Markup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['Complete Marketing &amp; Branding Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete SEO On-Page Optimization &amp; Schema Markup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Marketing &amp; Branding Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does SEO On-Page Optimization &amp; Schema Markup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ab3bf40b-aff5-52aa-9831-424bf0c61fbf</t>
+          <t>b61d0d45-f019-5134-9763-b69b75b59bd6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1713,47 +1713,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Premium Care Option 13</t>
+          <t>Employee Background Verification (Criminal &amp; Education)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3299</v>
+        <v>1199</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
+          <t>Address physical verification, court record checks, and university degree verification.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>['Professional Staffing &amp; HR Services Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Employee Background Verification (Criminal &amp; Education) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['Complete Staffing &amp; HR Services Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Employee Background Verification (Criminal &amp; Education) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Employee Background Verification (Criminal &amp; Education) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b61d0d45-f019-5134-9763-b69b75b59bd6</t>
+          <t>f2de5783-e16d-5c82-8474-430e0e7015cc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1768,47 +1768,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Premium Care Option 16</t>
+          <t>Exit Interview &amp; Full &amp; Final Settlement Processing</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3599</v>
+        <v>999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
+          <t>Managing notice period handovers, leave encashment calculations, and clearance approvals.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['Professional Staffing &amp; HR Services Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Exit Interview &amp; Full &amp; Final Settlement Processing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Complete Staffing &amp; HR Services Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Exit Interview &amp; Full &amp; Final Settlement Processing procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Exit Interview &amp; Full &amp; Final Settlement Processing take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ef6118e1-648b-5c1a-babf-6f4a12842388</t>
+          <t>7eb034ef-66d5-5be7-9fb2-4cabe9ff84fe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1823,47 +1823,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Premium Care Option 20</t>
+          <t>Mid-Level Executive Candidate Sourcing &amp; Screening</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3999</v>
+        <v>3499</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
+          <t>Filtering CVs, conducting preliminary technical interviews, and shortlisting top candidates.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>['Professional Staffing &amp; HR Services Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Mid-Level Executive Candidate Sourcing &amp; Screening procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['Complete Staffing &amp; HR Services Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Mid-Level Executive Candidate Sourcing &amp; Screening procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Mid-Level Executive Candidate Sourcing &amp; Screening take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f2de5783-e16d-5c82-8474-430e0e7015cc</t>
+          <t>ab3bf40b-aff5-52aa-9831-424bf0c61fbf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1878,47 +1878,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Premium Care Option 21</t>
+          <t>Payroll Processing &amp; Salary Slip Generation</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4099</v>
+        <v>1499</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
+          <t>Monthly salary calculation, PF/ESI deductions, and automated digital payslip delivery.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>['Professional Staffing &amp; HR Services Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Payroll Processing &amp; Salary Slip Generation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['Complete Staffing &amp; HR Services Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Payroll Processing &amp; Salary Slip Generation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Payroll Processing &amp; Salary Slip Generation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7eb034ef-66d5-5be7-9fb2-4cabe9ff84fe</t>
+          <t>ef6118e1-648b-5c1a-babf-6f4a12842388</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1933,40 +1933,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Staffing &amp; HR Services Premium Care Option 9</t>
+          <t>POSH Act Workplace Harassment Compliance Training</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2899</v>
+        <v>2999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Specialized high-end Staffing &amp; HR Services service tailored to specific client needs with extended guarantee.</t>
+          <t>Internal committee formation guidelines and interactive employee sensitivity workshop.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>['Professional Staffing &amp; HR Services Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional POSH Act Workplace Harassment Compliance Training procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['Complete Staffing &amp; HR Services Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete POSH Act Workplace Harassment Compliance Training procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Staffing &amp; HR Services Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does POSH Act Workplace Harassment Compliance Training take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1988,40 +1988,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Virtual Assistant Premium Care Option 12</t>
+          <t>Customer Support Chat &amp; Email Rep (Daily Shift)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3199</v>
+        <v>2499</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
+          <t>Answering customer queries, resolving tickets on Zendesk/Freshdesk with SLA.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>['Professional Virtual Assistant Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Customer Support Chat &amp; Email Rep (Daily Shift) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['Complete Virtual Assistant Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Customer Support Chat &amp; Email Rep (Daily Shift) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 240 minutes.', 'question': 'How long does Customer Support Chat &amp; Email Rep (Daily Shift) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -2043,40 +2043,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Virtual Assistant Premium Care Option 22</t>
+          <t>Data Entry &amp; Web Research Virtual Specialist</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4199</v>
+        <v>999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
+          <t>Accurate spreadsheet data entry, web scraping, and database updating.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>['Professional Virtual Assistant Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Data Entry &amp; Web Research Virtual Specialist procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['Complete Virtual Assistant Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Data Entry &amp; Web Research Virtual Specialist procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Data Entry &amp; Web Research Virtual Specialist take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -2098,40 +2098,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Virtual Assistant Premium Care Option 4</t>
+          <t>Executive Calendar &amp; Travel Booking Assistant</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2399</v>
+        <v>1499</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Specialized high-end Virtual Assistant service tailored to specific client needs with extended guarantee.</t>
+          <t>Coordinating Zoom calls, managing flight/hotel bookings, and itinerary preparation.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>['Professional Virtual Assistant Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Executive Calendar &amp; Travel Booking Assistant procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['Complete Virtual Assistant Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Executive Calendar &amp; Travel Booking Assistant procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Virtual Assistant Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Executive Calendar &amp; Travel Booking Assistant take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
